--- a/sampleprojects/CorporateTax/excel/states/NV_corp.xlsx
+++ b/sampleprojects/CorporateTax/excel/states/NV_corp.xlsx
@@ -60,7 +60,7 @@
     <t>Has physical presence in Nevada; has_physical_presence == true AND below threshold</t>
   </si>
   <si>
-    <t>result.has_physical_presence_nv and result.nv_gross_revenue &lt; result.nv_commerce_tax_threshold</t>
+    <t>result.has_physical_presence_nv and nv_result.gross_revenue &lt; nv_result.commerce_tax_threshold</t>
   </si>
   <si>
     <t>Y</t>
@@ -72,13 +72,13 @@
     <t>Has physical presence and exceeds threshold; has_physical_presence == true AND exceeds threshold</t>
   </si>
   <si>
-    <t>result.has_physical_presence_nv and result.nv_gross_revenue &gt;= result.nv_commerce_tax_threshold</t>
+    <t>result.has_physical_presence_nv and nv_result.gross_revenue &gt;= nv_result.commerce_tax_threshold</t>
   </si>
   <si>
     <t>Has economic nexus and exceeds threshold; has_economic_nexus == true AND exceeds threshold</t>
   </si>
   <si>
-    <t>result.nv_gross_revenue &gt;= result.nv_economic_nexus_threshold and result.nv_gross_revenue &gt;= result.nv_commerce_tax_threshold</t>
+    <t>nv_result.gross_revenue &gt;= result.nv_economic_nexus_threshold and nv_result.gross_revenue &gt;= nv_result.commerce_tax_threshold</t>
   </si>
   <si>
     <t>ACTIONS: COMMENTS</t>
@@ -90,7 +90,7 @@
     <t>Physical presence but below threshold - no Commerce Tax due</t>
   </si>
   <si>
-    <t>set result.nv_qualifies_for_exemption = true; set result.nv_commerce_tax = 0.0; set result.state_tax = 0.0;</t>
+    <t>set nv_result.qualifies_for_exemption = true; set nv_result.commerce_tax = 0.0; set result.state_tax = 0.0;</t>
   </si>
   <si>
     <t>X</t>
@@ -99,7 +99,7 @@
     <t>Physical nexus and above threshold - Commerce Tax required</t>
   </si>
   <si>
-    <t>set result.nv_qualifies_for_exemption = false;</t>
+    <t>set nv_result.qualifies_for_exemption = false;</t>
   </si>
   <si>
     <t>Economic nexus and above threshold - Commerce Tax required</t>
@@ -108,7 +108,7 @@
     <t>No nexus - no filing required</t>
   </si>
   <si>
-    <t>set result.nv_qualifies_for_exemption = true; set result.nv_commerce_tax = 0.0; set result.state_tax = 0.0; set result.state_refund_or_owed = result.state_payments;</t>
+    <t>set nv_result.qualifies_for_exemption = true; set nv_result.commerce_tax = 0.0; set result.state_tax = 0.0; set result.state_refund_or_owed = result.state_payments;</t>
   </si>
   <si>
     <t>DT: Calculate NV Income Adjustments</t>
@@ -123,7 +123,7 @@
     <t>Has nexus with Nevada; has_economic_nexus == true OR has_physical_presence == true</t>
   </si>
   <si>
-    <t>result.has_physical_presence_nv or result.nv_gross_revenue &gt;= result.nv_economic_nexus_threshold</t>
+    <t>result.has_physical_presence_nv or nv_result.gross_revenue &gt;= result.nv_economic_nexus_threshold</t>
   </si>
   <si>
     <t>Nevada has NO corporate income tax</t>
@@ -150,91 +150,91 @@
     <t>Financial Services (NAICS 52)</t>
   </si>
   <si>
-    <t>result.nv_business_classification == financial</t>
+    <t>nv_result.business_classification == financial</t>
   </si>
   <si>
     <t>Mining (NAICS 21)</t>
   </si>
   <si>
-    <t>result.nv_business_classification == mining</t>
+    <t>nv_result.business_classification == mining</t>
   </si>
   <si>
     <t>Utilities (NAICS 22)</t>
   </si>
   <si>
-    <t>result.nv_business_classification == utilities</t>
+    <t>nv_result.business_classification == utilities</t>
   </si>
   <si>
     <t>Professional Services (NAICS 54)</t>
   </si>
   <si>
-    <t>result.nv_business_classification == professional</t>
+    <t>nv_result.business_classification == professional</t>
   </si>
   <si>
     <t>Retail Trade (NAICS 44-45)</t>
   </si>
   <si>
-    <t>result.nv_business_classification == retail</t>
+    <t>nv_result.business_classification == retail</t>
   </si>
   <si>
     <t>Manufacturing (NAICS 31-33)</t>
   </si>
   <si>
-    <t>result.nv_business_classification == manufacturing</t>
+    <t>nv_result.business_classification == manufacturing</t>
   </si>
   <si>
     <t>Wholesale Trade (NAICS 42)</t>
   </si>
   <si>
-    <t>result.nv_business_classification == wholesale</t>
+    <t>nv_result.business_classification == wholesale</t>
   </si>
   <si>
     <t>Financial Services: 0.331% (highest rate)</t>
   </si>
   <si>
-    <t>set result.nv_commerce_tax_rate = result.nv_financial_services_rate;</t>
+    <t>set nv_result.commerce_tax_rate = nv_result.financial_services_rate;</t>
   </si>
   <si>
     <t>Mining: 0.262%</t>
   </si>
   <si>
-    <t>set result.nv_commerce_tax_rate = result.nv_mining_rate;</t>
+    <t>set nv_result.commerce_tax_rate = nv_result.mining_rate;</t>
   </si>
   <si>
     <t>Utilities: 0.266%</t>
   </si>
   <si>
-    <t>set result.nv_commerce_tax_rate = result.nv_utilities_rate;</t>
+    <t>set nv_result.commerce_tax_rate = nv_result.utilities_rate;</t>
   </si>
   <si>
     <t>Professional Services: 0.128%</t>
   </si>
   <si>
-    <t>set result.nv_commerce_tax_rate = result.nv_professional_services_rate;</t>
+    <t>set nv_result.commerce_tax_rate = nv_result.professional_services_rate;</t>
   </si>
   <si>
     <t>Retail Trade: 0.091%</t>
   </si>
   <si>
-    <t>set result.nv_commerce_tax_rate = result.nv_retail_trade_rate;</t>
+    <t>set nv_result.commerce_tax_rate = nv_result.retail_trade_rate;</t>
   </si>
   <si>
     <t>Manufacturing: 0.091%</t>
   </si>
   <si>
-    <t>set result.nv_commerce_tax_rate = result.nv_manufacturing_rate;</t>
+    <t>set nv_result.commerce_tax_rate = nv_result.manufacturing_rate;</t>
   </si>
   <si>
     <t>Wholesale Trade: 0.101%</t>
   </si>
   <si>
-    <t>set result.nv_commerce_tax_rate = result.nv_wholesale_trade_rate;</t>
+    <t>set nv_result.commerce_tax_rate = nv_result.wholesale_trade_rate;</t>
   </si>
   <si>
     <t>Other Services: 0.051% (lowest rate)</t>
   </si>
   <si>
-    <t>set result.nv_commerce_tax_rate = result.nv_other_rate;</t>
+    <t>set nv_result.commerce_tax_rate = nv_result.other_rate;</t>
   </si>
   <si>
     <t>DT: Calculate NV Sitused Revenue</t>
@@ -264,19 +264,19 @@
     <t>Calculate Nevada-sitused revenue using market-based sourcing</t>
   </si>
   <si>
-    <t>set result.nv_sitused_revenue = result.total_revenue * result.apportionment_percentage; set result.nv_gross_revenue = result.nv_sitused_revenue;</t>
+    <t>set nv_result.sitused_revenue = result.total_revenue * result.apportionment_percentage; set nv_result.gross_revenue = nv_result.sitused_revenue;</t>
   </si>
   <si>
     <t>No apportionment - assume 100% Nevada if nexus exists</t>
   </si>
   <si>
-    <t>set result.nv_sitused_revenue = result.total_revenue; set result.nv_gross_revenue = result.total_revenue;</t>
+    <t>set nv_result.sitused_revenue = result.total_revenue; set nv_result.gross_revenue = result.total_revenue;</t>
   </si>
   <si>
     <t>No Nevada nexus - no revenue sitused to Nevada</t>
   </si>
   <si>
-    <t>set result.nv_sitused_revenue = 0.0; set result.nv_gross_revenue = 0.0;</t>
+    <t>set nv_result.sitused_revenue = 0.0; set nv_result.gross_revenue = 0.0;</t>
   </si>
   <si>
     <t>DT: Calculate NV State Tax</t>
@@ -294,25 +294,25 @@
     <t>Has nexus and exceeds $4M threshold; has_nexus AND gross_revenue &gt;= threshold</t>
   </si>
   <si>
-    <t>(result.has_physical_presence_nv or result.nv_gross_revenue &gt;= result.nv_economic_nexus_threshold) and result.nv_gross_revenue &gt;= result.nv_commerce_tax_threshold</t>
+    <t>(result.has_physical_presence_nv or nv_result.gross_revenue &gt;= result.nv_economic_nexus_threshold) and nv_result.gross_revenue &gt;= nv_result.commerce_tax_threshold</t>
   </si>
   <si>
     <t>Has nexus but below threshold; has_nexus AND gross_revenue &lt; threshold</t>
   </si>
   <si>
-    <t>(result.has_physical_presence_nv or result.nv_gross_revenue &gt;= result.nv_economic_nexus_threshold) and result.nv_gross_revenue &lt; result.nv_commerce_tax_threshold</t>
+    <t>(result.has_physical_presence_nv or nv_result.gross_revenue &gt;= result.nv_economic_nexus_threshold) and nv_result.gross_revenue &lt; nv_result.commerce_tax_threshold</t>
   </si>
   <si>
     <t>Calculate Commerce Tax on taxable revenue</t>
   </si>
   <si>
-    <t>set result.nv_taxable_revenue = the maximum of (result.nv_gross_revenue - result.nv_commerce_tax_threshold) and (0.0); set result.nv_commerce_tax = result.nv_taxable_revenue * result.nv_commerce_tax_rate; set result.nv_commerce_tax = the maximum of (result.nv_commerce_tax - result.state_credits) and (0.0); set result.state_tax = result.nv_commerce_tax; set result.state_refund_or_owed = result.state_payments - result.state_tax;</t>
+    <t>set nv_result.taxable_revenue = the maximum of (nv_result.gross_revenue - nv_result.commerce_tax_threshold) and (0.0); set nv_result.commerce_tax = nv_result.taxable_revenue * nv_result.commerce_tax_rate; set nv_result.commerce_tax = the maximum of (nv_result.commerce_tax - result.state_credits) and (0.0); set result.state_tax = nv_result.commerce_tax; set result.state_refund_or_owed = result.state_payments - result.state_tax;</t>
   </si>
   <si>
     <t>Below threshold - no Commerce Tax</t>
   </si>
   <si>
-    <t>set result.nv_qualifies_for_exemption = true; set result.nv_taxable_revenue = 0.0; set result.nv_commerce_tax = 0.0; set result.state_tax = 0.0; set result.state_refund_or_owed = result.state_payments;</t>
+    <t>set nv_result.qualifies_for_exemption = true; set nv_result.taxable_revenue = 0.0; set nv_result.commerce_tax = 0.0; set result.state_tax = 0.0; set result.state_refund_or_owed = result.state_payments;</t>
   </si>
   <si>
     <t>No nexus - no Commerce Tax</t>
@@ -360,13 +360,13 @@
     <t>Reference</t>
   </si>
   <si>
-    <t>apportionment</t>
+    <t>nv_apportionment</t>
   </si>
   <si>
     <t>(3 attributes)</t>
   </si>
   <si>
-    <t>nv_economic_nexus_threshold</t>
+    <t>economic_nexus_threshold</t>
   </si>
   <si>
     <t>double</t>
@@ -381,7 +381,7 @@
     <t>Nevada economic nexus: $100,000 in Nevada receipts (follows Wayfair standard)</t>
   </si>
   <si>
-    <t>nv_state_tax_rate</t>
+    <t>state_tax_rate</t>
   </si>
   <si>
     <t>0.0</t>
@@ -390,7 +390,7 @@
     <t>Nevada has NO corporate income tax (Commerce Tax is calculated separately)</t>
   </si>
   <si>
-    <t>nv_transaction_threshold</t>
+    <t>transaction_threshold</t>
   </si>
   <si>
     <t>integer</t>
@@ -402,13 +402,13 @@
     <t>Nevada economic nexus: 200 or more separate transactions</t>
   </si>
   <si>
-    <t>result</t>
+    <t>nv_result</t>
   </si>
   <si>
     <t>(16 attributes)</t>
   </si>
   <si>
-    <t>nv_business_classification</t>
+    <t>business_classification</t>
   </si>
   <si>
     <t>string</t>
@@ -420,13 +420,13 @@
     <t>Nevada business classification: financial, mining, retail, professional, manufacturing, other</t>
   </si>
   <si>
-    <t>nv_commerce_tax</t>
+    <t>commerce_tax</t>
   </si>
   <si>
     <t>Nevada Commerce Tax liability (NOT an income tax - based on gross receipts)</t>
   </si>
   <si>
-    <t>nv_commerce_tax_rate</t>
+    <t>commerce_tax_rate</t>
   </si>
   <si>
     <t>0.00051</t>
@@ -435,7 +435,7 @@
     <t>Nevada Commerce Tax rate based on industry classification (0.051% default for lowest tier)</t>
   </si>
   <si>
-    <t>nv_commerce_tax_threshold</t>
+    <t>commerce_tax_threshold</t>
   </si>
   <si>
     <t>4000000.0</t>
@@ -444,7 +444,7 @@
     <t>Nevada Commerce Tax threshold: $4,000,000 in Nevada gross revenue (2025)</t>
   </si>
   <si>
-    <t>nv_financial_services_rate</t>
+    <t>financial_services_rate</t>
   </si>
   <si>
     <t>0.00331</t>
@@ -453,13 +453,13 @@
     <t>Financial Services Commerce Tax rate: 0.331% (highest rate)</t>
   </si>
   <si>
-    <t>nv_gross_revenue</t>
+    <t>gross_revenue</t>
   </si>
   <si>
     <t>Nevada-sourced gross revenue for Commerce Tax (receipts from Nevada activities)</t>
   </si>
   <si>
-    <t>nv_manufacturing_rate</t>
+    <t>manufacturing_rate</t>
   </si>
   <si>
     <t>0.00091</t>
@@ -468,7 +468,7 @@
     <t>Manufacturing Commerce Tax rate: 0.091%</t>
   </si>
   <si>
-    <t>nv_mining_rate</t>
+    <t>mining_rate</t>
   </si>
   <si>
     <t>0.00262</t>
@@ -477,13 +477,13 @@
     <t>Mining Commerce Tax rate: 0.262%</t>
   </si>
   <si>
-    <t>nv_other_rate</t>
+    <t>other_rate</t>
   </si>
   <si>
     <t>Other Services Commerce Tax rate: 0.051% (lowest rate)</t>
   </si>
   <si>
-    <t>nv_professional_services_rate</t>
+    <t>professional_services_rate</t>
   </si>
   <si>
     <t>0.00128</t>
@@ -492,7 +492,7 @@
     <t>Professional, Scientific, Technical Services Commerce Tax rate: 0.128%</t>
   </si>
   <si>
-    <t>nv_qualifies_for_exemption</t>
+    <t>qualifies_for_exemption</t>
   </si>
   <si>
     <t>boolean</t>
@@ -504,25 +504,25 @@
     <t>Nevada gross revenue below $4M threshold - no Commerce Tax due</t>
   </si>
   <si>
-    <t>nv_retail_trade_rate</t>
+    <t>retail_trade_rate</t>
   </si>
   <si>
     <t>Retail Trade Commerce Tax rate: 0.091%</t>
   </si>
   <si>
-    <t>nv_sitused_revenue</t>
+    <t>sitused_revenue</t>
   </si>
   <si>
     <t>Nevada sitused revenue (gross revenue sourced to Nevada using market-based rules)</t>
   </si>
   <si>
-    <t>nv_taxable_revenue</t>
+    <t>taxable_revenue</t>
   </si>
   <si>
     <t>Taxable revenue for Commerce Tax (gross revenue minus $4M threshold)</t>
   </si>
   <si>
-    <t>nv_utilities_rate</t>
+    <t>utilities_rate</t>
   </si>
   <si>
     <t>0.00266</t>
@@ -531,7 +531,7 @@
     <t>Utilities Commerce Tax rate: 0.266%</t>
   </si>
   <si>
-    <t>nv_wholesale_trade_rate</t>
+    <t>wholesale_trade_rate</t>
   </si>
   <si>
     <t>0.00101</t>
@@ -1855,222 +1855,254 @@
       <c r="R8" s="1"/>
       <c r="S8" s="1"/>
     </row>
-    <row r="9">
-      <c r="A9" s="5">
+    <row r="10">
+      <c r="A10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10" s="1">
         <v>1</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-      <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
-      <c r="L9" s="3"/>
-      <c r="M9" s="3"/>
-      <c r="N9" s="3"/>
-      <c r="O9" s="3"/>
-      <c r="P9" s="3"/>
-      <c r="Q9" s="3"/>
-      <c r="R9" s="3"/>
-      <c r="S9" s="3"/>
+      <c r="E10" s="1">
+        <v>2</v>
+      </c>
+      <c r="F10" s="1">
+        <v>3</v>
+      </c>
+      <c r="G10" s="1">
+        <v>4</v>
+      </c>
+      <c r="H10" s="1">
+        <v>5</v>
+      </c>
+      <c r="I10" s="1">
+        <v>6</v>
+      </c>
+      <c r="J10" s="1">
+        <v>7</v>
+      </c>
+      <c r="K10" s="1">
+        <v>8</v>
+      </c>
+      <c r="L10" s="1">
+        <v>9</v>
+      </c>
+      <c r="M10" s="1">
+        <v>10</v>
+      </c>
+      <c r="N10" s="1">
+        <v>11</v>
+      </c>
+      <c r="O10" s="1">
+        <v>12</v>
+      </c>
+      <c r="P10" s="1">
+        <v>13</v>
+      </c>
+      <c r="Q10" s="1">
+        <v>14</v>
+      </c>
+      <c r="R10" s="1">
+        <v>15</v>
+      </c>
+      <c r="S10" s="1">
+        <v>16</v>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="5">
+        <v>1</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S11" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D13" s="4">
+        <v>1</v>
+      </c>
+      <c r="E13" s="4">
+        <v>2</v>
+      </c>
+      <c r="F13" s="4">
+        <v>3</v>
+      </c>
+      <c r="G13" s="4">
+        <v>4</v>
+      </c>
+      <c r="H13" s="4">
+        <v>5</v>
+      </c>
+      <c r="I13" s="4">
+        <v>6</v>
+      </c>
+      <c r="J13" s="4">
+        <v>7</v>
+      </c>
+      <c r="K13" s="4">
+        <v>8</v>
+      </c>
+      <c r="L13" s="4">
+        <v>9</v>
+      </c>
+      <c r="M13" s="4">
         <v>10</v>
       </c>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1" t="s">
+      <c r="N13" s="4">
         <v>11</v>
       </c>
-      <c r="D11" s="1">
+      <c r="O13" s="4">
+        <v>12</v>
+      </c>
+      <c r="P13" s="4">
+        <v>13</v>
+      </c>
+      <c r="Q13" s="4">
+        <v>14</v>
+      </c>
+      <c r="R13" s="4">
+        <v>15</v>
+      </c>
+      <c r="S13" s="4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5">
         <v>1</v>
       </c>
-      <c r="E11" s="1">
-        <v>2</v>
-      </c>
-      <c r="F11" s="1">
-        <v>3</v>
-      </c>
-      <c r="G11" s="1">
-        <v>4</v>
-      </c>
-      <c r="H11" s="1">
-        <v>5</v>
-      </c>
-      <c r="I11" s="1">
-        <v>6</v>
-      </c>
-      <c r="J11" s="1">
-        <v>7</v>
-      </c>
-      <c r="K11" s="1">
-        <v>8</v>
-      </c>
-      <c r="L11" s="1">
-        <v>9</v>
-      </c>
-      <c r="M11" s="1">
-        <v>10</v>
-      </c>
-      <c r="N11" s="1">
-        <v>11</v>
-      </c>
-      <c r="O11" s="1">
-        <v>12</v>
-      </c>
-      <c r="P11" s="1">
-        <v>13</v>
-      </c>
-      <c r="Q11" s="1">
-        <v>14</v>
-      </c>
-      <c r="R11" s="1">
-        <v>15</v>
-      </c>
-      <c r="S11" s="1">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5">
-        <v>1</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="L12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="N12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="O12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="P12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="S12" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D14" s="4">
-        <v>1</v>
-      </c>
-      <c r="E14" s="4">
-        <v>2</v>
-      </c>
-      <c r="F14" s="4">
-        <v>3</v>
-      </c>
-      <c r="G14" s="4">
-        <v>4</v>
-      </c>
-      <c r="H14" s="4">
-        <v>5</v>
-      </c>
-      <c r="I14" s="4">
-        <v>6</v>
-      </c>
-      <c r="J14" s="4">
-        <v>7</v>
-      </c>
-      <c r="K14" s="4">
-        <v>8</v>
-      </c>
-      <c r="L14" s="4">
-        <v>9</v>
-      </c>
-      <c r="M14" s="4">
-        <v>10</v>
-      </c>
-      <c r="N14" s="4">
-        <v>11</v>
-      </c>
-      <c r="O14" s="4">
-        <v>12</v>
-      </c>
-      <c r="P14" s="4">
-        <v>13</v>
-      </c>
-      <c r="Q14" s="4">
-        <v>14</v>
-      </c>
-      <c r="R14" s="4">
-        <v>15</v>
-      </c>
-      <c r="S14" s="4">
-        <v>16</v>
+      <c r="B14" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S14" s="2" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>36</v>
       </c>
       <c r="D15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E15" s="2" t="s">
-        <v>8</v>
-      </c>
       <c r="F15" s="2" t="s">
         <v>8</v>
       </c>
@@ -2114,67 +2146,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="5">
-        <v>2</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="L16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="N16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="O16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="P16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="S16" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="A1:S1"/>
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="A3:S3"/>
@@ -2183,9 +2156,8 @@
     <mergeCell ref="C6:S6"/>
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="C8:S8"/>
-    <mergeCell ref="C9:S9"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A13:B13"/>
   </mergeCells>
 </worksheet>
 </file>

--- a/sampleprojects/CorporateTax/excel/states/NV_corp.xlsx
+++ b/sampleprojects/CorporateTax/excel/states/NV_corp.xlsx
@@ -150,43 +150,43 @@
     <t>Financial Services (NAICS 52)</t>
   </si>
   <si>
-    <t>nv_result.business_classification == financial</t>
+    <t>nv_result.business_classification == "financial"</t>
   </si>
   <si>
     <t>Mining (NAICS 21)</t>
   </si>
   <si>
-    <t>nv_result.business_classification == mining</t>
+    <t>nv_result.business_classification == "mining"</t>
   </si>
   <si>
     <t>Utilities (NAICS 22)</t>
   </si>
   <si>
-    <t>nv_result.business_classification == utilities</t>
+    <t>nv_result.business_classification == "utilities"</t>
   </si>
   <si>
     <t>Professional Services (NAICS 54)</t>
   </si>
   <si>
-    <t>nv_result.business_classification == professional</t>
+    <t>nv_result.business_classification == "professional"</t>
   </si>
   <si>
     <t>Retail Trade (NAICS 44-45)</t>
   </si>
   <si>
-    <t>nv_result.business_classification == retail</t>
+    <t>nv_result.business_classification == "retail"</t>
   </si>
   <si>
     <t>Manufacturing (NAICS 31-33)</t>
   </si>
   <si>
-    <t>nv_result.business_classification == manufacturing</t>
+    <t>nv_result.business_classification == "manufacturing"</t>
   </si>
   <si>
     <t>Wholesale Trade (NAICS 42)</t>
   </si>
   <si>
-    <t>nv_result.business_classification == wholesale</t>
+    <t>nv_result.business_classification == "wholesale"</t>
   </si>
   <si>
     <t>Financial Services: 0.331% (highest rate)</t>
